--- a/Summer_Ridge_Master_Sheet.xlsx
+++ b/Summer_Ridge_Master_Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6633C2A2-9F00-4942-919B-29D63C4E9B8B}"/>
+  <xr:revisionPtr revIDLastSave="136" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A28AD59-97CB-4F70-8687-EDD74F94C192}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
+    <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
   <sheets>
     <sheet name="Elec" sheetId="1" r:id="rId1"/>
@@ -612,7 +612,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -635,58 +635,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3818,7 +3767,7 @@
         <v>25003169</v>
       </c>
       <c r="C4" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -3829,7 +3778,7 @@
         <v>25003215</v>
       </c>
       <c r="C5" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -3884,7 +3833,7 @@
         <v>25003200</v>
       </c>
       <c r="C10" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
@@ -3994,7 +3943,7 @@
         <v>25003165</v>
       </c>
       <c r="C20" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
@@ -4049,7 +3998,7 @@
         <v>25003226</v>
       </c>
       <c r="C25" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
@@ -4115,7 +4064,7 @@
         <v>25003181</v>
       </c>
       <c r="C31" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
@@ -4137,7 +4086,7 @@
         <v>25003180</v>
       </c>
       <c r="C33" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
@@ -4291,7 +4240,7 @@
         <v>25003248</v>
       </c>
       <c r="C47" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
@@ -4489,7 +4438,7 @@
         <v>25003290</v>
       </c>
       <c r="C65" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.45">
@@ -4709,7 +4658,7 @@
         <v>25003265</v>
       </c>
       <c r="C85" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.45">
@@ -4742,7 +4691,7 @@
         <v>25003217</v>
       </c>
       <c r="C88" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.45">
@@ -4775,7 +4724,7 @@
         <v>25003256</v>
       </c>
       <c r="C91" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.45">
@@ -4808,7 +4757,7 @@
         <v>25003250</v>
       </c>
       <c r="C94" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.45">
@@ -4830,7 +4779,7 @@
         <v>25003214</v>
       </c>
       <c r="C96" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.45">
@@ -4896,7 +4845,7 @@
         <v>25003247</v>
       </c>
       <c r="C102" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.45">
@@ -5369,7 +5318,7 @@
         <v>25003173</v>
       </c>
       <c r="C145" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.45">

--- a/Summer_Ridge_Master_Sheet.xlsx
+++ b/Summer_Ridge_Master_Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="136" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A28AD59-97CB-4F70-8687-EDD74F94C192}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C89DEF5B-AEEC-48BA-ADBE-176A3AA6FF97}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
+    <workbookView xWindow="43080" yWindow="-7455" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
   <sheets>
     <sheet name="Elec" sheetId="1" r:id="rId1"/>
@@ -988,7 +988,8 @@
     <col min="1" max="1" width="17.73046875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.86328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.86328125" customWidth="1"/>
-    <col min="4" max="4" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -3722,8 +3723,8 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
@@ -3745,7 +3746,7 @@
         <v>25003273</v>
       </c>
       <c r="C2" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -3756,7 +3757,7 @@
         <v>25003187</v>
       </c>
       <c r="C3" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -3789,7 +3790,7 @@
         <v>25003302</v>
       </c>
       <c r="C6" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
@@ -3811,7 +3812,7 @@
         <v>25003167</v>
       </c>
       <c r="C8" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
@@ -3844,7 +3845,7 @@
         <v>25003183</v>
       </c>
       <c r="C11" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
@@ -3877,7 +3878,7 @@
         <v>25003188</v>
       </c>
       <c r="C14" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
@@ -3888,7 +3889,7 @@
         <v>25003184</v>
       </c>
       <c r="C15" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
@@ -3899,7 +3900,7 @@
         <v>25003218</v>
       </c>
       <c r="C16" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
@@ -3910,7 +3911,7 @@
         <v>25003212</v>
       </c>
       <c r="C17" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
@@ -3921,7 +3922,7 @@
         <v>25003164</v>
       </c>
       <c r="C18" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
@@ -3932,7 +3933,7 @@
         <v>25003197</v>
       </c>
       <c r="C19" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
@@ -3954,7 +3955,7 @@
         <v>25000769</v>
       </c>
       <c r="C21" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
@@ -4009,7 +4010,7 @@
         <v>25003228</v>
       </c>
       <c r="C26" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
@@ -4053,7 +4054,7 @@
         <v>25003225</v>
       </c>
       <c r="C30" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">

--- a/Summer_Ridge_Master_Sheet.xlsx
+++ b/Summer_Ridge_Master_Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Summer Ridge/Estate Management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C89DEF5B-AEEC-48BA-ADBE-176A3AA6FF97}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="8_{61B75D5B-E2B9-4A15-B62A-CAAC6678E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9FB7259-DE41-44B7-8893-534D3CAF51D4}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-7455" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97778EF9-769A-4231-8D2B-397889BE3400}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Elec" sheetId="1" r:id="rId1"/>
     <sheet name="Gas" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Gas!$A$1:$C$152</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -635,7 +638,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4076,7 +4090,7 @@
         <v>25003208</v>
       </c>
       <c r="C32" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
@@ -4164,7 +4178,7 @@
         <v>25003207</v>
       </c>
       <c r="C40" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
@@ -4186,7 +4200,7 @@
         <v>25003244</v>
       </c>
       <c r="C42" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
@@ -4208,7 +4222,7 @@
         <v>25003253</v>
       </c>
       <c r="C44" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
@@ -4230,7 +4244,7 @@
         <v>25003201</v>
       </c>
       <c r="C46" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.45">
@@ -5400,6 +5414,9 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B152">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>